--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_tarapaca.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_tarapaca.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>30.4462721577244</v>
+      </c>
+      <c r="C2">
         <v>22.93491493215357</v>
-      </c>
-      <c r="C2">
-        <v>30.4462721577244</v>
       </c>
       <c r="D2">
         <v>4.360164417257339</v>
       </c>
       <c r="E2">
-        <v>14.95288657448858</v>
+        <v>19.85006944814135</v>
       </c>
       <c r="F2">
         <v>65.19704397737007</v>
       </c>
       <c r="G2">
-        <v>19.85006944814135</v>
+        <v>14.95288657448858</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>42.03554076181784</v>
+      </c>
+      <c r="C3">
         <v>12.90768528709097</v>
-      </c>
-      <c r="C3">
-        <v>42.03554076181784</v>
       </c>
       <c r="D3">
         <v>7.747322449828429</v>
       </c>
       <c r="E3">
-        <v>8.330590253114119</v>
+        <v>27.12964085861298</v>
       </c>
       <c r="F3">
-        <v>64.5397688882729</v>
+        <v>64.53976888827289</v>
       </c>
       <c r="G3">
-        <v>27.12964085861298</v>
+        <v>8.330590253114117</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>40.00407166123778</v>
+      </c>
+      <c r="C4">
         <v>20.20561889250814</v>
-      </c>
-      <c r="C4">
-        <v>40.00407166123778</v>
       </c>
       <c r="D4">
         <v>4.94911838790932</v>
       </c>
       <c r="E4">
-        <v>12.61198297223457</v>
+        <v>24.96982019188004</v>
       </c>
       <c r="F4">
         <v>62.41819683588538</v>
       </c>
       <c r="G4">
-        <v>24.96982019188004</v>
+        <v>12.61198297223457</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>46.02368866328257</v>
+      </c>
+      <c r="C5">
         <v>40.77834179357022</v>
-      </c>
-      <c r="C5">
-        <v>46.02368866328257</v>
       </c>
       <c r="D5">
         <v>2.452282157676349</v>
       </c>
       <c r="E5">
+        <v>24.63768115942029</v>
+      </c>
+      <c r="F5">
+        <v>53.53260869565218</v>
+      </c>
+      <c r="G5">
         <v>21.82971014492754</v>
-      </c>
-      <c r="F5">
-        <v>53.53260869565217</v>
-      </c>
-      <c r="G5">
-        <v>24.63768115942029</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>40.48780487804878</v>
+      </c>
+      <c r="C6">
         <v>50</v>
-      </c>
-      <c r="C6">
-        <v>40.48780487804878</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6">
-        <v>26.24839948783611</v>
+        <v>21.25480153649168</v>
       </c>
       <c r="F6">
         <v>52.49679897567221</v>
       </c>
       <c r="G6">
-        <v>21.25480153649168</v>
+        <v>26.24839948783611</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>50.06802721088436</v>
+      </c>
+      <c r="C7">
         <v>33.12925170068027</v>
-      </c>
-      <c r="C7">
-        <v>50.06802721088436</v>
       </c>
       <c r="D7">
         <v>3.018480492813142</v>
       </c>
       <c r="E7">
-        <v>18.08392127738581</v>
+        <v>27.33011511325659</v>
       </c>
       <c r="F7">
         <v>54.58596360935759</v>
       </c>
       <c r="G7">
-        <v>27.33011511325659</v>
+        <v>18.08392127738581</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>41.69175195665262</v>
+      </c>
+      <c r="C8">
         <v>31.99879590608067</v>
-      </c>
-      <c r="C8">
-        <v>41.69175195665262</v>
       </c>
       <c r="D8">
         <v>3.125117591721543</v>
       </c>
       <c r="E8">
-        <v>18.42287694974004</v>
+        <v>24.00346620450606</v>
       </c>
       <c r="F8">
-        <v>57.57365684575391</v>
+        <v>57.5736568457539</v>
       </c>
       <c r="G8">
-        <v>24.00346620450607</v>
+        <v>18.42287694974003</v>
       </c>
     </row>
   </sheetData>
